--- a/erp-server/erp-server-plm/src/main/resources/excel/productPlanTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productPlanTemplate.xlsx
@@ -18,10 +18,41 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
-    <t>年份</t>
-  </si>
-  <si>
-    <t>产品经理</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>年份</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>产品经理</t>
+    </r>
   </si>
   <si>
     <t>所属品牌</t>
@@ -42,7 +73,26 @@
     <t>三代规划（721原则）</t>
   </si>
   <si>
-    <t>产品名称</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>产品名称</t>
+    </r>
   </si>
   <si>
     <t>产品名称（英文）</t>
@@ -218,7 +268,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -673,7 +723,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -682,10 +732,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -694,7 +744,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -703,13 +753,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -818,8 +868,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1172,12 +1225,43 @@
   <sheetPr/>
   <dimension ref="A1:BH1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
+    <col min="8" max="8" width="14.375" customWidth="1"/>
+    <col min="18" max="18" width="12.5" customWidth="1"/>
+    <col min="19" max="19" width="13.125" customWidth="1"/>
+    <col min="20" max="20" width="14.375" customWidth="1"/>
+    <col min="22" max="22" width="11.125" customWidth="1"/>
+    <col min="23" max="23" width="10.25" customWidth="1"/>
+    <col min="24" max="24" width="15.125" customWidth="1"/>
+    <col min="25" max="25" width="17.375" customWidth="1"/>
+    <col min="27" max="27" width="13.75" customWidth="1"/>
+    <col min="28" max="28" width="12.25" customWidth="1"/>
+    <col min="29" max="29" width="14.375" customWidth="1"/>
+    <col min="31" max="31" width="13.5" customWidth="1"/>
+    <col min="32" max="32" width="15.625" customWidth="1"/>
+    <col min="33" max="33" width="16.25" customWidth="1"/>
+    <col min="34" max="34" width="17" customWidth="1"/>
+    <col min="35" max="35" width="14" customWidth="1"/>
+    <col min="36" max="36" width="10.375" customWidth="1"/>
+    <col min="37" max="37" width="11.125" customWidth="1"/>
+    <col min="38" max="38" width="11" customWidth="1"/>
+    <col min="39" max="39" width="10.375" customWidth="1"/>
+    <col min="40" max="40" width="10.75" customWidth="1"/>
+    <col min="41" max="41" width="11.625" customWidth="1"/>
+    <col min="42" max="42" width="10.125" customWidth="1"/>
+    <col min="43" max="43" width="11.25" customWidth="1"/>
+    <col min="44" max="44" width="11.125" customWidth="1"/>
+    <col min="45" max="45" width="10.875" customWidth="1"/>
+    <col min="46" max="46" width="10" customWidth="1"/>
+    <col min="47" max="47" width="11.375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:60">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -1198,7 +1282,7 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -1356,6 +1440,42 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
+      <formula1>"常规款,利润款,流量款,爆款,王炸款,概念款,公关款"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV$1:BG$1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999999990000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V$1:V$1048576 W$1:W$1048576 AJ$1:AU$1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999999000</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
+      <formula1>"新品,老品"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
+      <formula1>"开发一代,储备一代,研究一代"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U$1:U$1048576">
+      <formula1>"Shopify,京东,Shopee,Walmart,速卖通,抖音/今日头条/鲁班,淘宝,阿里巴巴,有赞微商城,亚马逊,其他,B2B,小红书,拼多多,天猫,京东自营厂送"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH$1:AH$1048576">
+      <formula1>"春季,夏季,秋季,冬季"</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AE$1:AG$1048576">
+      <formula1>25569</formula1>
+      <formula2>72686</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:Y$1048576">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z$1:AA$1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999999</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productPlanTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productPlanTemplate.xlsx
@@ -41,39 +41,6 @@
   </si>
   <si>
     <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>产品经理</t>
-    </r>
-  </si>
-  <si>
-    <t>所属品牌</t>
-  </si>
-  <si>
-    <t>产品分类</t>
-  </si>
-  <si>
-    <t>产品等级</t>
-  </si>
-  <si>
-    <t>产品款品</t>
-  </si>
-  <si>
-    <t>新品/老品</t>
-  </si>
-  <si>
-    <t>三代规划（721原则）</t>
-  </si>
-  <si>
-    <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
@@ -91,7 +58,40 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>产品名称</t>
+      <t>产品经理</t>
+    </r>
+  </si>
+  <si>
+    <t>所属品牌</t>
+  </si>
+  <si>
+    <t>产品分类</t>
+  </si>
+  <si>
+    <t>产品等级</t>
+  </si>
+  <si>
+    <t>产品款品</t>
+  </si>
+  <si>
+    <t>新品/老品升级</t>
+  </si>
+  <si>
+    <t>三代规划（721原则）</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>产品名称（中文）</t>
     </r>
   </si>
   <si>
@@ -1444,6 +1444,26 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
       <formula1>"常规款,利润款,流量款,爆款,王炸款,概念款,公关款"</formula1>
     </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AE$1:AG$1048576">
+      <formula1>25569</formula1>
+      <formula2>72686</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
+      <formula1>"新品,老品"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z$1:AA$1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH$1:AH$1048576">
+      <formula1>"春季,夏季,秋季,冬季"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U$1:U$1048576">
+      <formula1>"Shopify,京东,Shopee,Walmart,速卖通,抖音/今日头条/鲁班,淘宝,阿里巴巴,有赞微商城,亚马逊,其他,B2B,小红书,拼多多,天猫,京东自营厂送"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
+      <formula1>"开发一代,储备一代,研究一代"</formula1>
+    </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV$1:BG$1048576">
       <formula1>0</formula1>
       <formula2>9999999999999990000</formula2>
@@ -1452,28 +1472,8 @@
       <formula1>0</formula1>
       <formula2>999999999999999000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
-      <formula1>"新品,老品"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
-      <formula1>"开发一代,储备一代,研究一代"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U$1:U$1048576">
-      <formula1>"Shopify,京东,Shopee,Walmart,速卖通,抖音/今日头条/鲁班,淘宝,阿里巴巴,有赞微商城,亚马逊,其他,B2B,小红书,拼多多,天猫,京东自营厂送"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH$1:AH$1048576">
-      <formula1>"春季,夏季,秋季,冬季"</formula1>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AE$1:AG$1048576">
-      <formula1>25569</formula1>
-      <formula2>72686</formula2>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:Y$1048576">
       <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z$1:AA$1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999999</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productPlanTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productPlanTemplate.xlsx
@@ -81,6 +81,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -173,76 +180,76 @@
     <t>计划上市时间</t>
   </si>
   <si>
-    <t>一月销售额</t>
-  </si>
-  <si>
-    <t>二月销售额</t>
-  </si>
-  <si>
-    <t>三月销售额</t>
-  </si>
-  <si>
-    <t>四月销售额</t>
-  </si>
-  <si>
-    <t>五月销售额</t>
-  </si>
-  <si>
-    <t>六月销售额</t>
-  </si>
-  <si>
-    <t>七月销售额</t>
-  </si>
-  <si>
-    <t>八月销售额</t>
-  </si>
-  <si>
-    <t>九月销售额</t>
-  </si>
-  <si>
-    <t>十月销售额</t>
-  </si>
-  <si>
-    <t>十一月销售额</t>
-  </si>
-  <si>
-    <t>十二月销售额</t>
-  </si>
-  <si>
-    <t>一月销量</t>
-  </si>
-  <si>
-    <t>二月销量</t>
-  </si>
-  <si>
-    <t>三月销量</t>
-  </si>
-  <si>
-    <t>四月销量</t>
-  </si>
-  <si>
-    <t>五月销量</t>
-  </si>
-  <si>
-    <t>六月销量</t>
-  </si>
-  <si>
-    <t>七月销量</t>
-  </si>
-  <si>
-    <t>八月销量</t>
-  </si>
-  <si>
-    <t>九月销量</t>
-  </si>
-  <si>
-    <t>十月销量</t>
-  </si>
-  <si>
-    <t>十一月销量</t>
-  </si>
-  <si>
-    <t>十二月销量</t>
+    <t>1月销售额</t>
+  </si>
+  <si>
+    <t>2月销售额</t>
+  </si>
+  <si>
+    <t>3月销售额</t>
+  </si>
+  <si>
+    <t>4月销售额</t>
+  </si>
+  <si>
+    <t>5月销售额</t>
+  </si>
+  <si>
+    <t>6月销售额</t>
+  </si>
+  <si>
+    <t>7月销售额</t>
+  </si>
+  <si>
+    <t>8月销售额</t>
+  </si>
+  <si>
+    <t>9月销售额</t>
+  </si>
+  <si>
+    <t>10月销售额</t>
+  </si>
+  <si>
+    <t>11月销售额</t>
+  </si>
+  <si>
+    <t>12月销售额</t>
+  </si>
+  <si>
+    <t>1月销量</t>
+  </si>
+  <si>
+    <t>2月销量</t>
+  </si>
+  <si>
+    <t>3月销量</t>
+  </si>
+  <si>
+    <t>4月销量</t>
+  </si>
+  <si>
+    <t>5月销量</t>
+  </si>
+  <si>
+    <t>6月销量</t>
+  </si>
+  <si>
+    <t>7月销量</t>
+  </si>
+  <si>
+    <t>8月销量</t>
+  </si>
+  <si>
+    <t>9月销量</t>
+  </si>
+  <si>
+    <t>10月销量</t>
+  </si>
+  <si>
+    <t>11月销量</t>
+  </si>
+  <si>
+    <t>12月销量</t>
   </si>
   <si>
     <t>其他备注</t>
@@ -1440,23 +1447,18 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="10">
+  <dataValidations count="13">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
+      <formula1>"新品,老品"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
+      <formula1>"Ulanz,中性,U-Selec,VIJI"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
       <formula1>"常规款,利润款,流量款,爆款,王炸款,概念款,公关款"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AE$1:AG$1048576">
-      <formula1>25569</formula1>
-      <formula2>72686</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
-      <formula1>"新品,老品"</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z$1:AA$1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH$1:AH$1048576">
-      <formula1>"春季,夏季,秋季,冬季"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
+      <formula1>"S,A,B,C,D"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U$1:U$1048576">
       <formula1>"Shopify,京东,Shopee,Walmart,速卖通,抖音/今日头条/鲁班,淘宝,阿里巴巴,有赞微商城,亚马逊,其他,B2B,小红书,拼多多,天猫,京东自营厂送"</formula1>
@@ -1464,16 +1466,30 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
       <formula1>"开发一代,储备一代,研究一代"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV$1:BG$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V$1:V$1048576 W$1:W$1048576 AJ2:AU1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999999000</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD$1:AD$1048576">
+      <formula1>"自研发,外采,委外设计,贴牌,联合设计"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH$1:AH$1048576">
+      <formula1>"春季,夏季,秋季,冬季"</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AE$1:AG$1048576">
+      <formula1>25569</formula1>
+      <formula2>72686</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2:BG1048576">
       <formula1>0</formula1>
       <formula2>9999999999999990000</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V$1:V$1048576 W$1:W$1048576 AJ$1:AU$1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999999000</formula2>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:Y$1048576">
       <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z$1:AA$1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999999</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productPlanTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productPlanTemplate.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <r>
       <rPr>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>其他备注</t>
+  </si>
+  <si>
+    <t>Ulanzi</t>
   </si>
 </sst>
 </file>
@@ -1230,8 +1233,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BH1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:BH3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="14.375" customWidth="1"/>
@@ -1446,13 +1449,18 @@
         <v>59</v>
       </c>
     </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="13">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
-      <formula1>"新品,老品"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:Y$1048576">
+      <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
-      <formula1>"Ulanz,中性,U-Selec,VIJI"</formula1>
+      <formula1>"Ulanzi,中性,U-Select,VIJIM"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
       <formula1>"常规款,利润款,流量款,爆款,王炸款,概念款,公关款"</formula1>
@@ -1460,18 +1468,21 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
       <formula1>"S,A,B,C,D"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U$1:U$1048576">
-      <formula1>"Shopify,京东,Shopee,Walmart,速卖通,抖音/今日头条/鲁班,淘宝,阿里巴巴,有赞微商城,亚马逊,其他,B2B,小红书,拼多多,天猫,京东自营厂送"</formula1>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V$1:V$1048576 W$1:W$1048576 AJ2:AU1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999999000</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
+      <formula1>"新品,老品"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD$1:AD$1048576">
+      <formula1>"自研发,外采,委外设计,贴牌,联合设计"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
       <formula1>"开发一代,储备一代,研究一代"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V$1:V$1048576 W$1:W$1048576 AJ2:AU1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999999000</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD$1:AD$1048576">
-      <formula1>"自研发,外采,委外设计,贴牌,联合设计"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U$1:U$1048576">
+      <formula1>"Shopify,京东,Shopee,Walmart,速卖通,抖音/今日头条/鲁班,淘宝,阿里巴巴,有赞微商城,亚马逊,其他,B2B,小红书,拼多多,天猫,京东自营厂送"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH$1:AH$1048576">
       <formula1>"春季,夏季,秋季,冬季"</formula1>
@@ -1483,9 +1494,6 @@
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2:BG1048576">
       <formula1>0</formula1>
       <formula2>9999999999999990000</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:Y$1048576">
-      <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z$1:AA$1048576">
       <formula1>0</formula1>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productPlanTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productPlanTemplate.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <r>
       <rPr>
@@ -253,9 +253,6 @@
   </si>
   <si>
     <t>其他备注</t>
-  </si>
-  <si>
-    <t>Ulanzi</t>
   </si>
 </sst>
 </file>
@@ -1233,8 +1230,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BH3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <dimension ref="A1:BH1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="14.375" customWidth="1"/>
@@ -1449,40 +1446,32 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="3:3">
-      <c r="C3" t="s">
-        <v>60</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="13">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:Y$1048576">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
       <formula1>"Ulanzi,中性,U-Select,VIJIM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
+      <formula1>"新品,老品"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
+      <formula1>"S,A,B,C,D"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
       <formula1>"常规款,利润款,流量款,爆款,王炸款,概念款,公关款"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
-      <formula1>"S,A,B,C,D"</formula1>
-    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V$1:V$1048576 W$1:W$1048576 AJ2:AU1048576">
       <formula1>0</formula1>
       <formula2>999999999999999000</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
-      <formula1>"新品,老品"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD$1:AD$1048576">
-      <formula1>"自研发,外采,委外设计,贴牌,联合设计"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
       <formula1>"开发一代,储备一代,研究一代"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U$1:U$1048576">
       <formula1>"Shopify,京东,Shopee,Walmart,速卖通,抖音/今日头条/鲁班,淘宝,阿里巴巴,有赞微商城,亚马逊,其他,B2B,小红书,拼多多,天猫,京东自营厂送"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD$1:AD$1048576">
+      <formula1>"自研发,外采,委外设计,贴牌,联合设计"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH$1:AH$1048576">
       <formula1>"春季,夏季,秋季,冬季"</formula1>
@@ -1491,13 +1480,16 @@
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2:BG1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999999990000</formula2>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:Y$1048576">
+      <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z$1:AA$1048576">
       <formula1>0</formula1>
       <formula2>999999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2:BG1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999999990000</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productPlanTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productPlanTemplate.xlsx
@@ -4,19 +4,32 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <r>
       <rPr>
@@ -68,6 +81,9 @@
     <t>产品分类</t>
   </si>
   <si>
+    <t>应用分类</t>
+  </si>
+  <si>
     <t>产品等级</t>
   </si>
   <si>
@@ -258,7 +274,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -281,55 +297,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -374,6 +354,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -419,7 +414,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -434,49 +450,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,121 +588,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -625,21 +641,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -672,6 +673,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -730,148 +746,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -885,52 +901,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1230,41 +1246,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BI1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="7" max="7" width="12.375" customWidth="1"/>
-    <col min="8" max="8" width="14.375" customWidth="1"/>
-    <col min="18" max="18" width="12.5" customWidth="1"/>
-    <col min="19" max="19" width="13.125" customWidth="1"/>
-    <col min="20" max="20" width="14.375" customWidth="1"/>
-    <col min="22" max="22" width="11.125" customWidth="1"/>
-    <col min="23" max="23" width="10.25" customWidth="1"/>
-    <col min="24" max="24" width="15.125" customWidth="1"/>
-    <col min="25" max="25" width="17.375" customWidth="1"/>
-    <col min="27" max="27" width="13.75" customWidth="1"/>
-    <col min="28" max="28" width="12.25" customWidth="1"/>
-    <col min="29" max="29" width="14.375" customWidth="1"/>
-    <col min="31" max="31" width="13.5" customWidth="1"/>
-    <col min="32" max="32" width="15.625" customWidth="1"/>
-    <col min="33" max="33" width="16.25" customWidth="1"/>
-    <col min="34" max="34" width="17" customWidth="1"/>
-    <col min="35" max="35" width="14" customWidth="1"/>
-    <col min="36" max="36" width="10.375" customWidth="1"/>
-    <col min="37" max="37" width="11.125" customWidth="1"/>
-    <col min="38" max="38" width="11" customWidth="1"/>
-    <col min="39" max="39" width="10.375" customWidth="1"/>
-    <col min="40" max="40" width="10.75" customWidth="1"/>
-    <col min="41" max="41" width="11.625" customWidth="1"/>
-    <col min="42" max="42" width="10.125" customWidth="1"/>
-    <col min="43" max="43" width="11.25" customWidth="1"/>
-    <col min="44" max="44" width="11.125" customWidth="1"/>
-    <col min="45" max="45" width="10.875" customWidth="1"/>
-    <col min="46" max="46" width="10" customWidth="1"/>
-    <col min="47" max="47" width="11.375" customWidth="1"/>
+    <col min="8" max="8" width="12.375" customWidth="1"/>
+    <col min="9" max="9" width="14.375" customWidth="1"/>
+    <col min="19" max="19" width="12.5" customWidth="1"/>
+    <col min="20" max="20" width="13.125" customWidth="1"/>
+    <col min="21" max="21" width="14.375" customWidth="1"/>
+    <col min="23" max="23" width="11.125" customWidth="1"/>
+    <col min="24" max="24" width="10.25" customWidth="1"/>
+    <col min="25" max="25" width="15.125" customWidth="1"/>
+    <col min="26" max="26" width="17.375" customWidth="1"/>
+    <col min="28" max="28" width="13.75" customWidth="1"/>
+    <col min="29" max="29" width="12.25" customWidth="1"/>
+    <col min="30" max="30" width="14.375" customWidth="1"/>
+    <col min="32" max="32" width="13.5" customWidth="1"/>
+    <col min="33" max="33" width="15.625" customWidth="1"/>
+    <col min="34" max="34" width="16.25" customWidth="1"/>
+    <col min="35" max="35" width="17" customWidth="1"/>
+    <col min="36" max="36" width="14" customWidth="1"/>
+    <col min="37" max="37" width="10.375" customWidth="1"/>
+    <col min="38" max="38" width="11.125" customWidth="1"/>
+    <col min="39" max="39" width="11" customWidth="1"/>
+    <col min="40" max="40" width="10.375" customWidth="1"/>
+    <col min="41" max="41" width="10.75" customWidth="1"/>
+    <col min="42" max="42" width="11.625" customWidth="1"/>
+    <col min="43" max="43" width="10.125" customWidth="1"/>
+    <col min="44" max="44" width="11.25" customWidth="1"/>
+    <col min="45" max="45" width="11.125" customWidth="1"/>
+    <col min="46" max="46" width="10.875" customWidth="1"/>
+    <col min="47" max="47" width="10" customWidth="1"/>
+    <col min="48" max="48" width="11.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60">
+    <row r="1" spans="1:61">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1289,10 +1305,10 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -1444,6 +1460,9 @@
       </c>
       <c r="BH1" t="s">
         <v>59</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1451,43 +1470,43 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
       <formula1>"Ulanzi,中性,U-Select,VIJIM"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
+      <formula1>"S,A,B,C,D"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
+      <formula1>"常规款,利润款,流量款,爆款,王炸款,概念款,公关款"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
       <formula1>"新品,老品"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
-      <formula1>"S,A,B,C,D"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
+      <formula1>"开发一代,储备一代,研究一代"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
-      <formula1>"常规款,利润款,流量款,爆款,王炸款,概念款,公关款"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V$1:V$1048576">
+      <formula1>"Shopify,京东,Shopee,Walmart,速卖通,抖音/今日头条/鲁班,淘宝,阿里巴巴,有赞微商城,亚马逊,其他,B2B,小红书,拼多多,天猫,京东自营厂送"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V$1:V$1048576 W$1:W$1048576 AJ2:AU1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE$1:AE$1048576">
+      <formula1>"自研发,外采,委外设计,贴牌,联合设计"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576">
+      <formula1>"春季,夏季,秋季,冬季"</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ$1:AJ$1048576 AF$1:AH$1048576">
+      <formula1>25569</formula1>
+      <formula2>72686</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W$1:X$1048576 AK2:AV1048576">
       <formula1>0</formula1>
       <formula2>999999999999999000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
-      <formula1>"开发一代,储备一代,研究一代"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U$1:U$1048576">
-      <formula1>"Shopify,京东,Shopee,Walmart,速卖通,抖音/今日头条/鲁班,淘宝,阿里巴巴,有赞微商城,亚马逊,其他,B2B,小红书,拼多多,天猫,京东自营厂送"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD$1:AD$1048576">
-      <formula1>"自研发,外采,委外设计,贴牌,联合设计"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH$1:AH$1048576">
-      <formula1>"春季,夏季,秋季,冬季"</formula1>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AE$1:AG$1048576">
-      <formula1>25569</formula1>
-      <formula2>72686</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:Y$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y$1:Z$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z$1:AA$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA$1:AB$1048576">
       <formula1>0</formula1>
       <formula2>999999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2:BG1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:BH1048576">
       <formula1>0</formula1>
       <formula2>9999999999999990000</formula2>
     </dataValidation>
